--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395676</v>
+        <v>121395683</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>74708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446339</v>
+        <v>446346</v>
       </c>
       <c r="R2" t="n">
-        <v>6732961</v>
+        <v>6732975</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395781</v>
+        <v>121395734</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>4766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446373</v>
+        <v>446341</v>
       </c>
       <c r="R4" t="n">
-        <v>6732994</v>
+        <v>6732961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395734</v>
+        <v>121395794</v>
       </c>
       <c r="B5" t="n">
-        <v>4766</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446341</v>
+        <v>446368</v>
       </c>
       <c r="R5" t="n">
-        <v>6732961</v>
+        <v>6732993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395794</v>
+        <v>121395676</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>5189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446368</v>
+        <v>446339</v>
       </c>
       <c r="R6" t="n">
-        <v>6732993</v>
+        <v>6732961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395825</v>
+        <v>121395782</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446338</v>
+        <v>446340</v>
       </c>
       <c r="R7" t="n">
-        <v>6732962</v>
+        <v>6732965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395782</v>
+        <v>121395825</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446340</v>
+        <v>446338</v>
       </c>
       <c r="R8" t="n">
-        <v>6732965</v>
+        <v>6732962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395683</v>
+        <v>121395781</v>
       </c>
       <c r="B9" t="n">
-        <v>74708</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446346</v>
+        <v>446373</v>
       </c>
       <c r="R9" t="n">
-        <v>6732975</v>
+        <v>6732994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395823</v>
+        <v>121395676</v>
       </c>
       <c r="B3" t="n">
-        <v>74700</v>
+        <v>5189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446327</v>
+        <v>446339</v>
       </c>
       <c r="R3" t="n">
-        <v>6733028</v>
+        <v>6732961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395676</v>
+        <v>121395782</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446339</v>
+        <v>446340</v>
       </c>
       <c r="R6" t="n">
-        <v>6732961</v>
+        <v>6732965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395782</v>
+        <v>121395825</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446340</v>
+        <v>446338</v>
       </c>
       <c r="R7" t="n">
-        <v>6732965</v>
+        <v>6732962</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395825</v>
+        <v>121395781</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446338</v>
+        <v>446373</v>
       </c>
       <c r="R8" t="n">
-        <v>6732962</v>
+        <v>6732994</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395781</v>
+        <v>121395823</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>74700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446373</v>
+        <v>446327</v>
       </c>
       <c r="R9" t="n">
-        <v>6732994</v>
+        <v>6733028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395683</v>
+        <v>121395781</v>
       </c>
       <c r="B2" t="n">
-        <v>74708</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446346</v>
+        <v>446373</v>
       </c>
       <c r="R2" t="n">
-        <v>6732975</v>
+        <v>6732994</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395676</v>
+        <v>121395683</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>74710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446339</v>
+        <v>446346</v>
       </c>
       <c r="R3" t="n">
-        <v>6732961</v>
+        <v>6732975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395734</v>
+        <v>121395676</v>
       </c>
       <c r="B4" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446341</v>
+        <v>446339</v>
       </c>
       <c r="R4" t="n">
         <v>6732961</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395794</v>
+        <v>121395782</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446368</v>
+        <v>446340</v>
       </c>
       <c r="R5" t="n">
-        <v>6732993</v>
+        <v>6732965</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395782</v>
+        <v>121395794</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446340</v>
+        <v>446368</v>
       </c>
       <c r="R6" t="n">
-        <v>6732965</v>
+        <v>6732993</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395825</v>
+        <v>121395734</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>4766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446338</v>
+        <v>446341</v>
       </c>
       <c r="R7" t="n">
-        <v>6732962</v>
+        <v>6732961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395781</v>
+        <v>121395825</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446373</v>
+        <v>446338</v>
       </c>
       <c r="R8" t="n">
-        <v>6732994</v>
+        <v>6732962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>121395823</v>
       </c>
       <c r="B9" t="n">
-        <v>74700</v>
+        <v>74702</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395781</v>
+        <v>121395676</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>5189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446373</v>
+        <v>446339</v>
       </c>
       <c r="R2" t="n">
-        <v>6732994</v>
+        <v>6732961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395683</v>
+        <v>121395823</v>
       </c>
       <c r="B3" t="n">
-        <v>74710</v>
+        <v>74702</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446346</v>
+        <v>446327</v>
       </c>
       <c r="R3" t="n">
-        <v>6732975</v>
+        <v>6733028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395676</v>
+        <v>121395734</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446339</v>
+        <v>446341</v>
       </c>
       <c r="R4" t="n">
         <v>6732961</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395782</v>
+        <v>121395794</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446340</v>
+        <v>446368</v>
       </c>
       <c r="R5" t="n">
-        <v>6732965</v>
+        <v>6732993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395794</v>
+        <v>121395683</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446368</v>
+        <v>446346</v>
       </c>
       <c r="R6" t="n">
-        <v>6732993</v>
+        <v>6732975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395734</v>
+        <v>121395825</v>
       </c>
       <c r="B7" t="n">
-        <v>4766</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446341</v>
+        <v>446338</v>
       </c>
       <c r="R7" t="n">
-        <v>6732961</v>
+        <v>6732962</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395825</v>
+        <v>121395782</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446338</v>
+        <v>446340</v>
       </c>
       <c r="R8" t="n">
-        <v>6732962</v>
+        <v>6732965</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395823</v>
+        <v>121395781</v>
       </c>
       <c r="B9" t="n">
-        <v>74702</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446327</v>
+        <v>446373</v>
       </c>
       <c r="R9" t="n">
-        <v>6733028</v>
+        <v>6732994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395676</v>
+        <v>121395781</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446339</v>
+        <v>446373</v>
       </c>
       <c r="R2" t="n">
-        <v>6732961</v>
+        <v>6732994</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395823</v>
+        <v>121395676</v>
       </c>
       <c r="B3" t="n">
-        <v>74702</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446327</v>
+        <v>446339</v>
       </c>
       <c r="R3" t="n">
-        <v>6733028</v>
+        <v>6732961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395734</v>
+        <v>121395825</v>
       </c>
       <c r="B4" t="n">
-        <v>4766</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446341</v>
+        <v>446338</v>
       </c>
       <c r="R4" t="n">
-        <v>6732961</v>
+        <v>6732962</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395794</v>
+        <v>121395823</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>74705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446368</v>
+        <v>446327</v>
       </c>
       <c r="R5" t="n">
-        <v>6732993</v>
+        <v>6733028</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395683</v>
+        <v>121395734</v>
       </c>
       <c r="B6" t="n">
-        <v>74710</v>
+        <v>4769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446346</v>
+        <v>446341</v>
       </c>
       <c r="R6" t="n">
-        <v>6732975</v>
+        <v>6732961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395825</v>
+        <v>121395794</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446338</v>
+        <v>446368</v>
       </c>
       <c r="R7" t="n">
-        <v>6732962</v>
+        <v>6732993</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
         <v>121395782</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395781</v>
+        <v>121395683</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>74713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446373</v>
+        <v>446346</v>
       </c>
       <c r="R9" t="n">
-        <v>6732994</v>
+        <v>6732975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395676</v>
+        <v>121395823</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>74705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446339</v>
+        <v>446327</v>
       </c>
       <c r="R3" t="n">
-        <v>6732961</v>
+        <v>6733028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395825</v>
+        <v>121395794</v>
       </c>
       <c r="B4" t="n">
-        <v>5172</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446338</v>
+        <v>446368</v>
       </c>
       <c r="R4" t="n">
-        <v>6732962</v>
+        <v>6732993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395823</v>
+        <v>121395782</v>
       </c>
       <c r="B5" t="n">
-        <v>74705</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446327</v>
+        <v>446340</v>
       </c>
       <c r="R5" t="n">
-        <v>6733028</v>
+        <v>6732965</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395734</v>
+        <v>121395683</v>
       </c>
       <c r="B6" t="n">
-        <v>4769</v>
+        <v>74713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446341</v>
+        <v>446346</v>
       </c>
       <c r="R6" t="n">
-        <v>6732961</v>
+        <v>6732975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395794</v>
+        <v>121395676</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>5192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446368</v>
+        <v>446339</v>
       </c>
       <c r="R7" t="n">
-        <v>6732993</v>
+        <v>6732961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395782</v>
+        <v>121395734</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>4769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446340</v>
+        <v>446341</v>
       </c>
       <c r="R8" t="n">
-        <v>6732965</v>
+        <v>6732961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395683</v>
+        <v>121395825</v>
       </c>
       <c r="B9" t="n">
-        <v>74713</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446346</v>
+        <v>446338</v>
       </c>
       <c r="R9" t="n">
-        <v>6732975</v>
+        <v>6732962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395781</v>
+        <v>121395825</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446373</v>
+        <v>446338</v>
       </c>
       <c r="R2" t="n">
-        <v>6732994</v>
+        <v>6732962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395823</v>
+        <v>121395676</v>
       </c>
       <c r="B3" t="n">
-        <v>74705</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446327</v>
+        <v>446339</v>
       </c>
       <c r="R3" t="n">
-        <v>6733028</v>
+        <v>6732961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395794</v>
+        <v>121395823</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>74706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446368</v>
+        <v>446327</v>
       </c>
       <c r="R4" t="n">
-        <v>6732993</v>
+        <v>6733028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395782</v>
+        <v>121395794</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446340</v>
+        <v>446368</v>
       </c>
       <c r="R5" t="n">
-        <v>6732965</v>
+        <v>6732993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395683</v>
+        <v>121395734</v>
       </c>
       <c r="B6" t="n">
-        <v>74713</v>
+        <v>4769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446346</v>
+        <v>446341</v>
       </c>
       <c r="R6" t="n">
-        <v>6732975</v>
+        <v>6732961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395676</v>
+        <v>121395782</v>
       </c>
       <c r="B7" t="n">
-        <v>5192</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446339</v>
+        <v>446340</v>
       </c>
       <c r="R7" t="n">
-        <v>6732961</v>
+        <v>6732965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395734</v>
+        <v>121395781</v>
       </c>
       <c r="B8" t="n">
-        <v>4769</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446341</v>
+        <v>446373</v>
       </c>
       <c r="R8" t="n">
-        <v>6732961</v>
+        <v>6732994</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395825</v>
+        <v>121395683</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
+        <v>74714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446338</v>
+        <v>446346</v>
       </c>
       <c r="R9" t="n">
-        <v>6732962</v>
+        <v>6732975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395823</v>
+        <v>121395782</v>
       </c>
       <c r="B4" t="n">
-        <v>74706</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446327</v>
+        <v>446340</v>
       </c>
       <c r="R4" t="n">
-        <v>6733028</v>
+        <v>6732965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>121395794</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395734</v>
+        <v>121395823</v>
       </c>
       <c r="B6" t="n">
-        <v>4769</v>
+        <v>74707</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446341</v>
+        <v>446327</v>
       </c>
       <c r="R6" t="n">
-        <v>6732961</v>
+        <v>6733028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395782</v>
+        <v>121395734</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>4769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446340</v>
+        <v>446341</v>
       </c>
       <c r="R7" t="n">
-        <v>6732965</v>
+        <v>6732961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
         <v>121395781</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>121395683</v>
       </c>
       <c r="B9" t="n">
-        <v>74714</v>
+        <v>74715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395825</v>
+        <v>121395781</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446338</v>
+        <v>446373</v>
       </c>
       <c r="R2" t="n">
-        <v>6732962</v>
+        <v>6732994</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395676</v>
+        <v>121395782</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446339</v>
+        <v>446340</v>
       </c>
       <c r="R3" t="n">
-        <v>6732961</v>
+        <v>6732965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395782</v>
+        <v>121395683</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>74715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446340</v>
+        <v>446346</v>
       </c>
       <c r="R4" t="n">
-        <v>6732965</v>
+        <v>6732975</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395794</v>
+        <v>121395825</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446368</v>
+        <v>446338</v>
       </c>
       <c r="R5" t="n">
-        <v>6732993</v>
+        <v>6732962</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395823</v>
+        <v>121395676</v>
       </c>
       <c r="B6" t="n">
-        <v>74707</v>
+        <v>5192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446327</v>
+        <v>446339</v>
       </c>
       <c r="R6" t="n">
-        <v>6733028</v>
+        <v>6732961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395734</v>
+        <v>121395794</v>
       </c>
       <c r="B7" t="n">
-        <v>4769</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446341</v>
+        <v>446368</v>
       </c>
       <c r="R7" t="n">
-        <v>6732961</v>
+        <v>6732993</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395781</v>
+        <v>121395823</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>74707</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446373</v>
+        <v>446327</v>
       </c>
       <c r="R8" t="n">
-        <v>6732994</v>
+        <v>6733028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395683</v>
+        <v>121395734</v>
       </c>
       <c r="B9" t="n">
-        <v>74715</v>
+        <v>4769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446346</v>
+        <v>446341</v>
       </c>
       <c r="R9" t="n">
-        <v>6732975</v>
+        <v>6732961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395781</v>
+        <v>121395794</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446373</v>
+        <v>446368</v>
       </c>
       <c r="R2" t="n">
-        <v>6732994</v>
+        <v>6732993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395683</v>
+        <v>121395823</v>
       </c>
       <c r="B4" t="n">
-        <v>74715</v>
+        <v>74707</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446346</v>
+        <v>446327</v>
       </c>
       <c r="R4" t="n">
-        <v>6732975</v>
+        <v>6733028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395794</v>
+        <v>121395734</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>4769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446368</v>
+        <v>446341</v>
       </c>
       <c r="R7" t="n">
-        <v>6732993</v>
+        <v>6732961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395823</v>
+        <v>121395683</v>
       </c>
       <c r="B8" t="n">
-        <v>74707</v>
+        <v>74715</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446327</v>
+        <v>446346</v>
       </c>
       <c r="R8" t="n">
-        <v>6733028</v>
+        <v>6732975</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395734</v>
+        <v>121395781</v>
       </c>
       <c r="B9" t="n">
-        <v>4769</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446341</v>
+        <v>446373</v>
       </c>
       <c r="R9" t="n">
-        <v>6732961</v>
+        <v>6732994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395794</v>
+        <v>121395782</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446368</v>
+        <v>446340</v>
       </c>
       <c r="R2" t="n">
-        <v>6732993</v>
+        <v>6732965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395782</v>
+        <v>121395676</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446340</v>
+        <v>446339</v>
       </c>
       <c r="R3" t="n">
-        <v>6732965</v>
+        <v>6732961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395823</v>
+        <v>121395825</v>
       </c>
       <c r="B4" t="n">
-        <v>74707</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446327</v>
+        <v>446338</v>
       </c>
       <c r="R4" t="n">
-        <v>6733028</v>
+        <v>6732962</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395825</v>
+        <v>121395734</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>4769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446338</v>
+        <v>446341</v>
       </c>
       <c r="R5" t="n">
-        <v>6732962</v>
+        <v>6732961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395676</v>
+        <v>121395781</v>
       </c>
       <c r="B6" t="n">
-        <v>5192</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446339</v>
+        <v>446373</v>
       </c>
       <c r="R6" t="n">
-        <v>6732961</v>
+        <v>6732994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395734</v>
+        <v>121395794</v>
       </c>
       <c r="B7" t="n">
-        <v>4769</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446341</v>
+        <v>446368</v>
       </c>
       <c r="R7" t="n">
-        <v>6732961</v>
+        <v>6732993</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395683</v>
+        <v>121395823</v>
       </c>
       <c r="B8" t="n">
-        <v>74715</v>
+        <v>74707</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446346</v>
+        <v>446327</v>
       </c>
       <c r="R8" t="n">
-        <v>6732975</v>
+        <v>6733028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395781</v>
+        <v>121395683</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>74715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446373</v>
+        <v>446346</v>
       </c>
       <c r="R9" t="n">
-        <v>6732994</v>
+        <v>6732975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395782</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395676</v>
+        <v>121395683</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>74722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446339</v>
+        <v>446346</v>
       </c>
       <c r="R3" t="n">
-        <v>6732961</v>
+        <v>6732975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395825</v>
+        <v>121395734</v>
       </c>
       <c r="B4" t="n">
-        <v>5172</v>
+        <v>4770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446338</v>
+        <v>446341</v>
       </c>
       <c r="R4" t="n">
-        <v>6732962</v>
+        <v>6732961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395734</v>
+        <v>121395823</v>
       </c>
       <c r="B5" t="n">
-        <v>4769</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446341</v>
+        <v>446327</v>
       </c>
       <c r="R5" t="n">
-        <v>6732961</v>
+        <v>6733028</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395781</v>
+        <v>121395825</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446373</v>
+        <v>446338</v>
       </c>
       <c r="R6" t="n">
-        <v>6732994</v>
+        <v>6732962</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395794</v>
+        <v>121395676</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446368</v>
+        <v>446339</v>
       </c>
       <c r="R7" t="n">
-        <v>6732993</v>
+        <v>6732961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395823</v>
+        <v>121395781</v>
       </c>
       <c r="B8" t="n">
-        <v>74707</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446327</v>
+        <v>446373</v>
       </c>
       <c r="R8" t="n">
-        <v>6733028</v>
+        <v>6732994</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395683</v>
+        <v>121395794</v>
       </c>
       <c r="B9" t="n">
-        <v>74715</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446346</v>
+        <v>446368</v>
       </c>
       <c r="R9" t="n">
-        <v>6732975</v>
+        <v>6732993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395782</v>
+        <v>121395683</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>74722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446340</v>
+        <v>446346</v>
       </c>
       <c r="R2" t="n">
-        <v>6732965</v>
+        <v>6732975</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395683</v>
+        <v>121395782</v>
       </c>
       <c r="B3" t="n">
-        <v>74722</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446346</v>
+        <v>446340</v>
       </c>
       <c r="R3" t="n">
-        <v>6732975</v>
+        <v>6732965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395825</v>
+        <v>121395823</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446338</v>
+        <v>446327</v>
       </c>
       <c r="R2" t="n">
-        <v>6732962</v>
+        <v>6733028</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395676</v>
+        <v>121395829</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446339</v>
+        <v>446401</v>
       </c>
       <c r="R3" t="n">
-        <v>6732961</v>
+        <v>6732996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395683</v>
+        <v>121395794</v>
       </c>
       <c r="B4" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446346</v>
+        <v>446368</v>
       </c>
       <c r="R4" t="n">
-        <v>6732975</v>
+        <v>6732993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395781</v>
+        <v>121395683</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446373</v>
+        <v>446346</v>
       </c>
       <c r="R5" t="n">
-        <v>6732994</v>
+        <v>6732975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1066,7 @@
         <v>121395734</v>
       </c>
       <c r="B6" t="n">
-        <v>4770</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395794</v>
+        <v>121395825</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446368</v>
+        <v>446338</v>
       </c>
       <c r="R7" t="n">
-        <v>6732993</v>
+        <v>6732962</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121395823</v>
+        <v>121395676</v>
       </c>
       <c r="B8" t="n">
-        <v>74714</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446327</v>
+        <v>446339</v>
       </c>
       <c r="R8" t="n">
-        <v>6733028</v>
+        <v>6732961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121395782</v>
+        <v>121395781</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446340</v>
+        <v>446373</v>
       </c>
       <c r="R9" t="n">
-        <v>6732965</v>
+        <v>6732994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,6 +1448,103 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121395782</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>V Finngruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>446340</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6732965</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61259-2023 artfynd.xlsx
+++ b/artfynd/A 61259-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395823</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395829</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395683</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395734</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395825</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395676</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395781</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>